--- a/public/dl/ke-6cge.xlsx
+++ b/public/dl/ke-6cge.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Mermas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Inventario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Checklist Mermas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,9 +19,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00 €"/>
+    <numFmt formatCode="+0.00;-0.00" numFmtId="164"/>
+    <numFmt formatCode="DD/MM/YYYY" numFmtId="165"/>
+    <numFmt formatCode="#,##0.00 €" numFmtId="166"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -194,57 +194,57 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="5" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="5" fontId="9" numFmtId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="5" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="5" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="6" fontId="10" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -609,8 +609,8 @@
   <dimension ref="B2:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -686,7 +686,7 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -700,14 +700,14 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="12"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
+    <col customWidth="1" max="7" min="7" width="16"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,7 +1131,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1145,12 +1145,12 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="22"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="30"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1449,14 +1449,14 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33" type="list">
       <formula1>"Caducidad,Mal estado,Sobreproducción,Error de preparación,Almacenaje incorrecto,Porcionado excesivo,Otro"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>